--- a/data/trans_orig/P1425-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2007</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489314</t>
+          <t>489221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>459686</t>
+          <t>459335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466554</t>
+          <t>466553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>952474</t>
+          <t>951773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960594</t>
+          <t>960504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>11345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>724702</t>
+          <t>724751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734454</t>
+          <t>733629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>615220</t>
+          <t>614149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624298</t>
+          <t>624318</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1343367</t>
+          <t>1344366</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1356734</t>
+          <t>1356913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>10873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>22125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620151</t>
+          <t>621351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634511</t>
+          <t>634495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>680344</t>
+          <t>678871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>688600</t>
+          <t>688767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307205</t>
+          <t>1306287</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321559</t>
+          <t>1321453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507444</t>
+          <t>506775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517175</t>
+          <t>517151</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>505157</t>
+          <t>504204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513872</t>
+          <t>513829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1016791</t>
+          <t>1015685</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1029646</t>
+          <t>1029825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20462</t>
+          <t>18463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>373774</t>
+          <t>372587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383792</t>
+          <t>383776</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393313</t>
+          <t>393193</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402236</t>
+          <t>402275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>770234</t>
+          <t>772233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>784704</t>
+          <t>784321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18797</t>
+          <t>18354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279510</t>
+          <t>279553</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289755</t>
+          <t>289891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333221</t>
+          <t>332246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341391</t>
+          <t>341274</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616720</t>
+          <t>617163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>629396</t>
+          <t>629933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>28793</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196011</t>
+          <t>197140</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206383</t>
+          <t>206442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313945</t>
+          <t>313809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328583</t>
+          <t>328699</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>515197</t>
+          <t>514998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532649</t>
+          <t>532851</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54004</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,82 +3148,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>36848</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>24563</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>50002</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>77580</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>61383</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>97777</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>36848</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>26157</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>50834</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>77580</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>61588</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>95599</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3222539</t>
+          <t>3222225</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3246442</t>
+          <t>3246849</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,82 +3261,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3261</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3342349</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3329195</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3354634</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6434</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6578161</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6557964</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6594358</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3261</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3342349</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3328363</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3353040</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6434</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6578161</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6560142</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6594153</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2012</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7499</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446647</t>
+          <t>446167</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453255</t>
+          <t>453250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>876844</t>
+          <t>876432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883483</t>
+          <t>883482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9550</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>679237</t>
+          <t>679080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686167</t>
+          <t>686158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604481</t>
+          <t>604604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287792</t>
+          <t>1287591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296353</t>
+          <t>1296352</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668734</t>
+          <t>668343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>695960</t>
+          <t>694817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707573</t>
+          <t>707564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1369421</t>
+          <t>1367226</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1385531</t>
+          <t>1385031</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>21576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24417</t>
+          <t>23754</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591966</t>
+          <t>593041</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609360</t>
+          <t>609334</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606200</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1204463</t>
+          <t>1205126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1222260</t>
+          <t>1222363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,39 +5133,39 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>10533</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10010</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418972</t>
+          <t>419501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428111</t>
+          <t>428373</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>447800</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,42 +5246,42 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>873128</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>866696</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>876189</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>873128</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>867219</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>876168</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302646</t>
+          <t>302097</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>346956</t>
+          <t>347281</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653762</t>
+          <t>653704</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662445</t>
+          <t>662731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12606</t>
+          <t>13185</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>237245</t>
+          <t>236666</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248792</t>
+          <t>248788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>370548</t>
+          <t>371534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384638</t>
+          <t>384620</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614126</t>
+          <t>614797</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>631255</t>
+          <t>632300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47551</t>
+          <t>47346</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13340</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32525</t>
+          <t>34047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40640</t>
+          <t>39692</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73422</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3379228</t>
+          <t>3379433</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3404801</t>
+          <t>3404196</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3522573</t>
+          <t>3521051</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3541758</t>
+          <t>3541752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6908455</t>
+          <t>6910423</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6941237</t>
+          <t>6942185</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de otros problemas mentales en 2016</t>
+          <t>Población con diagnóstico de otros problemas mentales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11999</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411502</t>
+          <t>411511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389862</t>
+          <t>388976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803858</t>
+          <t>803219</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813920</t>
+          <t>814219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>576830</t>
+          <t>577309</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588485</t>
+          <t>588443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558564</t>
+          <t>559072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1139993</t>
+          <t>1138853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151275</t>
+          <t>1151114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>14825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20709</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658449</t>
+          <t>658381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667185</t>
+          <t>667308</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>648592</t>
+          <t>646561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659184</t>
+          <t>658948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1309774</t>
+          <t>1310478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324626</t>
+          <t>1324521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16270</t>
+          <t>16079</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629778</t>
+          <t>629969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641936</t>
+          <t>641970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634520</t>
+          <t>635774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646995</t>
+          <t>646955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1271473</t>
+          <t>1270636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286933</t>
+          <t>1286382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467960</t>
+          <t>468871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476879</t>
+          <t>476878</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>484572</t>
+          <t>485346</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495690</t>
+          <t>495691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>959183</t>
+          <t>959032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>972379</t>
+          <t>971813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327193</t>
+          <t>327792</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366531</t>
+          <t>366784</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375863</t>
+          <t>375888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>698843</t>
+          <t>698196</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>709085</t>
+          <t>709166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9024</t>
+          <t>9812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>18702</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7473</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23235</t>
+          <t>24890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247974</t>
+          <t>247186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255424</t>
+          <t>255384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381460</t>
+          <t>381467</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396490</t>
+          <t>396465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>633932</t>
+          <t>632277</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649694</t>
+          <t>649736</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43640</t>
+          <t>45296</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23590</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>47721</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>50294</t>
+          <t>49228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>85810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3350710</t>
+          <t>3349054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373070</t>
+          <t>3371866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3496845</t>
+          <t>3496821</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3520952</t>
+          <t>3521891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6855326</t>
+          <t>6853082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6888598</t>
+          <t>6889664</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1425-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1425-Edad-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9780</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489221</t>
+          <t>488267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>459335</t>
+          <t>459539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466553</t>
+          <t>466555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>951773</t>
+          <t>952599</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960504</t>
+          <t>960591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>10420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>17010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>724751</t>
+          <t>725171</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733629</t>
+          <t>734446</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>614149</t>
+          <t>615074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624318</t>
+          <t>624414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1344366</t>
+          <t>1343972</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1356913</t>
+          <t>1356586</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22125</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621351</t>
+          <t>621233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634495</t>
+          <t>634788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>678871</t>
+          <t>679759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>688767</t>
+          <t>688778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306287</t>
+          <t>1304538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321453</t>
+          <t>1321164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506775</t>
+          <t>507357</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517151</t>
+          <t>517206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>504204</t>
+          <t>505344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>513829</t>
+          <t>513839</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1015685</t>
+          <t>1016965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1029825</t>
+          <t>1029745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>372587</t>
+          <t>372534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>383776</t>
+          <t>383772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>393193</t>
+          <t>393472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402275</t>
+          <t>402847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>772233</t>
+          <t>770567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>784321</t>
+          <t>784154</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10688</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279553</t>
+          <t>279587</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289891</t>
+          <t>289840</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332246</t>
+          <t>333045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341274</t>
+          <t>341280</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>617163</t>
+          <t>617347</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>629933</t>
+          <t>629980</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28793</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>197140</t>
+          <t>196660</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206442</t>
+          <t>206398</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>313809</t>
+          <t>312570</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>328699</t>
+          <t>328612</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>514998</t>
+          <t>514841</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532851</t>
+          <t>532605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29694</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>26169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50002</t>
+          <t>51608</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61383</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97777</t>
+          <t>96573</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3222225</t>
+          <t>3222640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3246849</t>
+          <t>3247132</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3329195</t>
+          <t>3327589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3354634</t>
+          <t>3353028</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6557964</t>
+          <t>6559168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6594358</t>
+          <t>6592790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446167</t>
+          <t>446616</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453250</t>
+          <t>453255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>876432</t>
+          <t>875932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>883482</t>
+          <t>883484</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>679080</t>
+          <t>678359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686158</t>
+          <t>686157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>604604</t>
+          <t>605276</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1287591</t>
+          <t>1287467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1296352</t>
+          <t>1296357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24211</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668343</t>
+          <t>668065</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680005</t>
+          <t>680014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>694817</t>
+          <t>694823</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707564</t>
+          <t>707642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1367226</t>
+          <t>1369251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1385031</t>
+          <t>1385813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593041</t>
+          <t>591702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>609317</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>606232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205126</t>
+          <t>1204900</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1222363</t>
+          <t>1222350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>10744</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10533</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>419501</t>
+          <t>418685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>428373</t>
+          <t>428387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866696</t>
+          <t>867741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876189</t>
+          <t>876099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>7764</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10078</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302097</t>
+          <t>302064</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>347281</t>
+          <t>346232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>653704</t>
+          <t>654496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>662731</t>
+          <t>662782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13185</t>
+          <t>13018</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>7614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5882,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236666</t>
+          <t>236833</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371534</t>
+          <t>371865</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384620</t>
+          <t>384639</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>614797</t>
+          <t>613765</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>632300</t>
+          <t>631216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>22727</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47346</t>
+          <t>47552</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34047</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71454</t>
+          <t>73379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3379433</t>
+          <t>3379227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3404196</t>
+          <t>3404052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3521051</t>
+          <t>3521334</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3541752</t>
+          <t>3541640</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6910423</t>
+          <t>6908498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6942185</t>
+          <t>6940359</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411511</t>
+          <t>410359</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388976</t>
+          <t>388955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803219</t>
+          <t>805114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814219</t>
+          <t>814224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15187</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577309</t>
+          <t>577176</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588443</t>
+          <t>588484</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>559072</t>
+          <t>559122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138853</t>
+          <t>1139661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151114</t>
+          <t>1151306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>658381</t>
+          <t>658153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667308</t>
+          <t>667252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646561</t>
+          <t>646820</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658948</t>
+          <t>658942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1310478</t>
+          <t>1311266</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324521</t>
+          <t>1324741</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13649</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8743</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>25455</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629969</t>
+          <t>629575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641970</t>
+          <t>641185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635774</t>
+          <t>635428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646955</t>
+          <t>647015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270636</t>
+          <t>1269670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286382</t>
+          <t>1286240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15735</t>
+          <t>15025</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468871</t>
+          <t>468944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476878</t>
+          <t>476883</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485346</t>
+          <t>485941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495691</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,7 +8225,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>959032</t>
+          <t>959742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>971813</t>
+          <t>971416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6538</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10978</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13896</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327792</t>
+          <t>327108</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366784</t>
+          <t>366844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375888</t>
+          <t>375842</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>698196</t>
+          <t>698203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>709166</t>
+          <t>709154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1614</t>
+          <t>1589</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9812</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247186</t>
+          <t>248006</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255384</t>
+          <t>255409</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381467</t>
+          <t>380470</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396465</t>
+          <t>395573</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>632277</t>
+          <t>634269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649736</t>
+          <t>650105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>23612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47721</t>
+          <t>47907</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>48836</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>85810</t>
+          <t>82304</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3349054</t>
+          <t>3349182</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371866</t>
+          <t>3372394</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3496821</t>
+          <t>3496635</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3521891</t>
+          <t>3520930</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6853082</t>
+          <t>6856588</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6889664</t>
+          <t>6890056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
